--- a/assets/constructions/examples/ctd_bs_cart_adj.xlsx
+++ b/assets/constructions/examples/ctd_bs_cart_adj.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,86 +544,114 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAC95-F16-CC06-R</t>
+          <t>R140.0-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>SANDVIK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CoroTurnⓇ 107 cartridge for turning</t>
+        </is>
+      </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>1.7</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>DER_UNKNOWN</t>
+          <t>COR_BORING_ROUND_METRIC:10</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ISO_CC0602H</t>
+          <t>ISO_TC0902H</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CC0602H</t>
+          <t>SAND_TC0902_H</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>ISO</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>0.04</v>
+      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MAC90-F20-TC11-R</t>
+          <t>MAC90-F16-CC06-L</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -633,7 +661,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
         <v>90</v>
@@ -662,13 +690,13 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ISO_TC1102H</t>
+          <t>ISO_CC0602H</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>TC1102H</t>
+          <t>CC0602H</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -679,7 +707,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -694,11 +722,25 @@
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
       </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>386.15</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>31654.22</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R142.0-10-09</t>
+          <t>R141.0-16-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -712,13 +754,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.23</v>
+        <v>7.5</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -732,18 +774,18 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>COR_BORING_ROUND_METRIC:10</t>
+          <t>COR_BORING_ROUND_METRIC:16</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ISO_TC0902H</t>
+          <t>ISO_TC1102H</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SAND_TC0902_H</t>
+          <t>SAND_TC1102_H</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -761,7 +803,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.039</v>
+        <v>0.14</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -771,159 +813,189 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R142.0-20-16</t>
+          <t>MAC95-F16-CC06-L</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CoroTurnⓇ 107 cartridge for turning</t>
-        </is>
-      </c>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-0.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="F5" t="n">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01</v>
+      </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>COR_BORING_ROUND_METRIC:20</t>
+          <t>DER_UNKNOWN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ISO_TC16T3H</t>
+          <t>ISO_CC0602H</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SAND_TC16T3_H</t>
+          <t>CC0602H</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>ISO</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0.283</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
+          <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>386.15</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>31654.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R141.0-10-09</t>
+          <t>MAC95-F16-CC06-R</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CoroTurnⓇ 107 cartridge for turning</t>
-        </is>
-      </c>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01</v>
+      </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>COR_BORING_ROUND_METRIC:10</t>
+          <t>DER_UNKNOWN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ISO_TC0902H</t>
+          <t>ISO_CC0602H</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SAND_TC0902_H</t>
+          <t>CC0602H</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>ISO</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.04</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
+          <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>386.15</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>31654.22</v>
       </c>
     </row>
   </sheetData>
